--- a/ხელფასები დელივერერს.xlsx
+++ b/ხელფასები დელივერერს.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766255D9-0DC5-4B46-91FF-ABC6A83EF803}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0E00C4-2757-4FCB-818C-7E817CFE8E3C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ხელფასები" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ხელფასები!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="65">
   <si>
     <t>თარიღი</t>
   </si>
@@ -219,6 +219,15 @@
   <si>
     <t>01001083359</t>
   </si>
+  <si>
+    <t>დავით</t>
+  </si>
+  <si>
+    <t>სვირავა</t>
+  </si>
+  <si>
+    <t>62003016407</t>
+  </si>
 </sst>
 </file>
 
@@ -391,7 +400,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -425,7 +434,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -713,23 +721,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P73"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="8.90625" style="11"/>
-    <col min="3" max="3" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.36328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.36328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" style="11"/>
-    <col min="8" max="8" width="10.36328125" customWidth="1"/>
-    <col min="9" max="9" width="10.36328125" style="18" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="10.36328125" customWidth="1"/>
-    <col min="12" max="12" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" style="11" customWidth="1"/>
-    <col min="14" max="14" width="8.90625" style="11"/>
-    <col min="15" max="16" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.90625" style="11"/>
+    <col min="1" max="2" width="8.88671875" style="11"/>
+    <col min="3" max="3" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="11"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="18" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" style="11" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="11"/>
+    <col min="15" max="16" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -754,17 +762,21 @@
       <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="C2" s="28">
-        <v>46143</v>
-      </c>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="27">
+        <v>46216</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="29">
-        <v>250</v>
+      <c r="F2" s="28">
+        <v>125</v>
+      </c>
+      <c r="G2" s="11">
+        <f>F2/0.98/0.8</f>
+        <v>159.43877551020407</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -773,120 +785,146 @@
       <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="C3" s="28">
-        <v>46156</v>
-      </c>
-      <c r="D3" s="29" t="s">
+      <c r="C3" s="27">
+        <v>46217</v>
+      </c>
+      <c r="D3" s="28" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="28">
         <v>1000</v>
+      </c>
+      <c r="G3" s="11">
+        <f t="shared" ref="G3:G8" si="0">F3/0.98/0.8</f>
+        <v>1275.5102040816325</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
-      <c r="J3" s="26"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="C4" s="28">
-        <v>46164</v>
-      </c>
-      <c r="D4" s="29" t="s">
+      <c r="C4" s="27">
+        <v>46222</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="28">
         <v>225</v>
+      </c>
+      <c r="G4" s="11">
+        <f t="shared" si="0"/>
+        <v>286.98979591836735</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="26"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="11"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="C5" s="28">
-        <v>46170</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="29">
+      <c r="C5" s="27">
+        <v>46225</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="28">
         <v>1200</v>
+      </c>
+      <c r="G5" s="11">
+        <f t="shared" si="0"/>
+        <v>1530.6122448979593</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="26"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="C6" s="28">
-        <v>46170</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="29">
-        <v>1000</v>
+      <c r="C6" s="27">
+        <v>46230</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="28">
+        <v>225</v>
+      </c>
+      <c r="G6" s="11">
+        <f t="shared" si="0"/>
+        <v>286.98979591836735</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="21"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
+      <c r="K6" s="11"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="C7" s="28">
-        <v>46171</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="29">
-        <v>225</v>
+      <c r="C7" s="27">
+        <v>46230</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="28">
+        <v>1200</v>
+      </c>
+      <c r="G7" s="11">
+        <f t="shared" si="0"/>
+        <v>1530.6122448979593</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
+      <c r="K7" s="11"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="29"/>
+      <c r="C8" s="27">
+        <v>46230</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="28">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="0"/>
+        <v>1275.5102040816325</v>
+      </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="20"/>
-      <c r="F9" s="29"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="11">
+        <f>SUM(G2:G8)</f>
+        <v>6345.6632653061224</v>
+      </c>
       <c r="I9" s="14"/>
       <c r="J9" s="15"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:14">
       <c r="C10" s="9"/>
@@ -895,6 +933,7 @@
       <c r="F10" s="8"/>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:14">
       <c r="C11" s="9"/>
@@ -903,6 +942,7 @@
       <c r="F11" s="8"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:14">
       <c r="C12" s="9"/>
@@ -912,6 +952,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="14"/>
       <c r="J12" s="15"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:14">
       <c r="C13" s="9"/>
@@ -920,6 +961,7 @@
       <c r="F13" s="8"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:14">
       <c r="C14" s="9"/>
@@ -928,6 +970,7 @@
       <c r="F14" s="8"/>
       <c r="I14" s="10"/>
       <c r="J14" s="16"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:14">
       <c r="C15" s="17"/>
@@ -936,6 +979,7 @@
       <c r="F15" s="16"/>
       <c r="I15" s="10"/>
       <c r="J15" s="16"/>
+      <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:14">
       <c r="C16" s="17"/>
@@ -944,6 +988,7 @@
       <c r="F16" s="16"/>
       <c r="I16" s="10"/>
       <c r="J16" s="16"/>
+      <c r="K16" s="11"/>
     </row>
     <row r="17" spans="3:16">
       <c r="C17" s="17"/>
@@ -952,6 +997,7 @@
       <c r="F17" s="16"/>
       <c r="I17" s="13"/>
       <c r="J17" s="14"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" spans="3:16">
       <c r="C18" s="17"/>
@@ -960,6 +1006,7 @@
       <c r="F18" s="16"/>
       <c r="I18" s="13"/>
       <c r="J18" s="14"/>
+      <c r="K18" s="11"/>
     </row>
     <row r="19" spans="3:16">
       <c r="C19" s="17"/>
@@ -968,10 +1015,8 @@
       <c r="F19" s="16"/>
       <c r="I19" s="13"/>
       <c r="J19" s="14"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="17"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="17"/>
     </row>
     <row r="20" spans="3:16">
       <c r="C20" s="17"/>
@@ -980,10 +1025,8 @@
       <c r="F20" s="16"/>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="17"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="17"/>
     </row>
     <row r="21" spans="3:16">
       <c r="C21" s="17"/>
@@ -992,10 +1035,8 @@
       <c r="F21" s="16"/>
       <c r="I21" s="13"/>
       <c r="J21" s="14"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="17"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="17"/>
     </row>
     <row r="22" spans="3:16">
       <c r="C22" s="17"/>
@@ -1004,10 +1045,8 @@
       <c r="F22" s="16"/>
       <c r="I22" s="13"/>
       <c r="J22" s="14"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="17"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="17"/>
     </row>
     <row r="23" spans="3:16">
       <c r="C23" s="17"/>
@@ -1016,10 +1055,8 @@
       <c r="F23" s="16"/>
       <c r="I23" s="13"/>
       <c r="J23" s="14"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="17"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="17"/>
     </row>
     <row r="24" spans="3:16">
       <c r="C24" s="17"/>
@@ -1028,9 +1065,8 @@
       <c r="F24" s="16"/>
       <c r="I24" s="13"/>
       <c r="J24" s="14"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="P24" s="17"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="17"/>
     </row>
     <row r="25" spans="3:16">
       <c r="C25" s="17"/>
@@ -1363,9 +1399,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1829,7 +1865,7 @@
         <f t="shared" si="0"/>
         <v>საბაცაგარეიშვილი</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1878,23 +1914,53 @@
     <row r="11" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+        <v>დავითსვირავა</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A12" t="str">
@@ -2073,10 +2139,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P69"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.453125" customWidth="1"/>
-    <col min="4" max="4" width="24.90625" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2159,18 +2225,18 @@
       </c>
       <c r="H2">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F2/0.8,ხელფასები!F2/0.8/0.98)</f>
-        <v>318.87755102040819</v>
+        <v>159.4387755102041</v>
       </c>
       <c r="I2" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F2/0.8/0.98*0.02)</f>
-        <v>6.3775510204081636</v>
+        <v>3.1887755102040818</v>
       </c>
       <c r="J2" s="5">
         <v>0</v>
       </c>
       <c r="K2" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C2))&gt;1,DAY(ხელფასები!C2),CONCATENATE("0",DAY(ხელფასები!C2))),"/",MONTH(ხელფასები!C2),"/",YEAR(ხელფასები!C2))</f>
-        <v>01/5/2026</v>
+        <v>13/7/2026</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,12,FALSE)</f>
@@ -2178,7 +2244,7 @@
       </c>
       <c r="M2">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F2/0.8*0.2,(ხელფასები!F2/0.8/0.98-ხელფასები!F2/0.8/0.98*0.02)*0.2)</f>
-        <v>62.5</v>
+        <v>31.25</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,14,FALSE)</f>
@@ -2235,7 +2301,7 @@
       </c>
       <c r="K3" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C3))&gt;1,DAY(ხელფასები!C3),CONCATENATE("0",DAY(ხელფასები!C3))),"/",MONTH(ხელფასები!C3),"/",YEAR(ხელფასები!C3))</f>
-        <v>14/5/2026</v>
+        <v>14/7/2026</v>
       </c>
       <c r="L3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,12,FALSE)</f>
@@ -2300,7 +2366,7 @@
       </c>
       <c r="K4" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C4))&gt;1,DAY(ხელფასები!C4),CONCATENATE("0",DAY(ხელფასები!C4))),"/",MONTH(ხელფასები!C4),"/",YEAR(ხელფასები!C4))</f>
-        <v>22/5/2026</v>
+        <v>19/7/2026</v>
       </c>
       <c r="L4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,12,FALSE)</f>
@@ -2326,19 +2392,19 @@
     <row r="5" spans="1:16">
       <c r="A5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$100,2,FALSE)</f>
-        <v>01003003707</v>
+        <v>62003016407</v>
       </c>
       <c r="B5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$120,3,FALSE)</f>
-        <v>ნანა</v>
+        <v>დავით</v>
       </c>
       <c r="C5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$120,4,FALSE)</f>
-        <v>კურცხალია</v>
+        <v>სვირავა</v>
       </c>
       <c r="D5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,5,FALSE)</f>
-        <v>თბილისი, მუხიანი მესამე მ/რ, კორპუსი 1</v>
+        <v>თბილისი</v>
       </c>
       <c r="E5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,6,FALSE)</f>
@@ -2365,7 +2431,7 @@
       </c>
       <c r="K5" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C5))&gt;1,DAY(ხელფასები!C5),CONCATENATE("0",DAY(ხელფასები!C5))),"/",MONTH(ხელფასები!C5),"/",YEAR(ხელფასები!C5))</f>
-        <v>28/5/2026</v>
+        <v>22/7/2026</v>
       </c>
       <c r="L5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,12,FALSE)</f>
@@ -2391,19 +2457,19 @@
     <row r="6" spans="1:16">
       <c r="A6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$100,2,FALSE)</f>
-        <v>01017025072</v>
+        <v>01009003935</v>
       </c>
       <c r="B6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$120,3,FALSE)</f>
-        <v>ზურაბი</v>
+        <v>ალექსანდრე</v>
       </c>
       <c r="C6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$120,4,FALSE)</f>
-        <v>თომაძე</v>
+        <v>ლეჟავა</v>
       </c>
       <c r="D6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,5,FALSE)</f>
-        <v>თბილისი გიგა ლორთქიფანიძის ქ. N 13 ფ. 2</v>
+        <v>თბილისი</v>
       </c>
       <c r="E6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,6,FALSE)</f>
@@ -2419,18 +2485,18 @@
       </c>
       <c r="H6">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F6/0.8,ხელფასები!F6/0.8/0.98)</f>
-        <v>1275.5102040816328</v>
+        <v>286.98979591836735</v>
       </c>
       <c r="I6" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F6/0.8/0.98*0.02)</f>
-        <v>25.510204081632654</v>
+        <v>5.7397959183673475</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
       </c>
       <c r="K6" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C6))&gt;1,DAY(ხელფასები!C6),CONCATENATE("0",DAY(ხელფასები!C6))),"/",MONTH(ხელფასები!C6),"/",YEAR(ხელფასები!C6))</f>
-        <v>28/5/2026</v>
+        <v>27/7/2026</v>
       </c>
       <c r="L6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,12,FALSE)</f>
@@ -2438,7 +2504,7 @@
       </c>
       <c r="M6">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F6/0.8*0.2,(ხელფასები!F6/0.8/0.98-ხელფასები!F6/0.8/0.98*0.02)*0.2)</f>
-        <v>250</v>
+        <v>56.25</v>
       </c>
       <c r="N6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,14,FALSE)</f>
@@ -2456,19 +2522,19 @@
     <row r="7" spans="1:16">
       <c r="A7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$100,2,FALSE)</f>
-        <v>01009003935</v>
+        <v>01003003707</v>
       </c>
       <c r="B7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$120,3,FALSE)</f>
-        <v>ალექსანდრე</v>
+        <v>ნანა</v>
       </c>
       <c r="C7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$120,4,FALSE)</f>
-        <v>ლეჟავა</v>
+        <v>კურცხალია</v>
       </c>
       <c r="D7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,5,FALSE)</f>
-        <v>თბილისი</v>
+        <v>თბილისი, მუხიანი მესამე მ/რ, კორპუსი 1</v>
       </c>
       <c r="E7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,6,FALSE)</f>
@@ -2484,18 +2550,18 @@
       </c>
       <c r="H7">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F7/0.8,ხელფასები!F7/0.8/0.98)</f>
-        <v>286.98979591836735</v>
+        <v>1530.6122448979593</v>
       </c>
       <c r="I7" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F7/0.8/0.98*0.02)</f>
-        <v>5.7397959183673475</v>
+        <v>30.612244897959187</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
       </c>
       <c r="K7" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C7))&gt;1,DAY(ხელფასები!C7),CONCATENATE("0",DAY(ხელფასები!C7))),"/",MONTH(ხელფასები!C7),"/",YEAR(ხელფასები!C7))</f>
-        <v>29/5/2026</v>
+        <v>27/7/2026</v>
       </c>
       <c r="L7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,12,FALSE)</f>
@@ -2503,7 +2569,7 @@
       </c>
       <c r="M7">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F7/0.8*0.2,(ხელფასები!F7/0.8/0.98-ხელფასები!F7/0.8/0.98*0.02)*0.2)</f>
-        <v>56.25</v>
+        <v>300</v>
       </c>
       <c r="N7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,14,FALSE)</f>
@@ -2519,66 +2585,66 @@
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8">
+      <c r="A8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$100,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="B8">
+        <v>01017025072</v>
+      </c>
+      <c r="B8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$120,3,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="C8">
+        <v>ზურაბი</v>
+      </c>
+      <c r="C8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$120,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D8">
+        <v>თომაძე</v>
+      </c>
+      <c r="D8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E8">
+        <v>თბილისი გიგა ლორთქიფანიძის ქ. N 13 ფ. 2</v>
+      </c>
+      <c r="E8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F8">
+        <v>268</v>
+      </c>
+      <c r="F8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="G8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F8/0.8,ხელფასები!F8/0.8/0.98)</f>
-        <v>0</v>
+        <v>1275.5102040816328</v>
       </c>
       <c r="I8" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F8/0.8/0.98*0.02)</f>
-        <v>0</v>
+        <v>25.510204081632654</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
       </c>
       <c r="K8" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C8))&gt;1,DAY(ხელფასები!C8),CONCATENATE("0",DAY(ხელფასები!C8))),"/",MONTH(ხელფასები!C8),"/",YEAR(ხელფასები!C8))</f>
-        <v>00/1/1900</v>
-      </c>
-      <c r="L8">
+        <v>27/7/2026</v>
+      </c>
+      <c r="L8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,12,FALSE)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M8">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F8/0.8*0.2,(ხელფასები!F8/0.8/0.98-ხელფასები!F8/0.8/0.98*0.02)*0.2)</f>
-        <v>0</v>
-      </c>
-      <c r="N8">
+        <v>250</v>
+      </c>
+      <c r="N8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,14,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,15,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D8,ხელფასები!E8),map!$A$1:$P$102,16,FALSE)</f>
         <v>0</v>
       </c>
@@ -6556,7 +6622,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -6591,7 +6657,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
